--- a/verification/cases/roundtrip/formulas_dynamic_arrays/init.xlsx
+++ b/verification/cases/roundtrip/formulas_dynamic_arrays/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/dynamic-arrays/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4B0331-BC53-1E48-BE56-D2F41678F07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71B97D82-EE7E-4C28-BF89-D140141526F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="4780" windowWidth="41900" windowHeight="21100" xr2:uid="{BB7BB86B-4264-B342-A646-A584C05166A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BB7BB86B-4264-B342-A646-A584C05166A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1652,7 +1652,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1675,26 +1675,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00A1EF2-BCA6-F243-9B8C-CA1D6B204217}">
   <dimension ref="B2:O701"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1706,7 +1706,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1720,7 +1720,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1732,7 +1732,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1784,7 +1784,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1798,7 +1798,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>23</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
@@ -1896,7 +1896,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>28</v>
       </c>
@@ -1912,7 +1912,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>33</v>
       </c>
@@ -1931,7 +1931,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>35</v>
       </c>
@@ -1948,7 +1948,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
@@ -1965,7 +1965,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>39</v>
       </c>
@@ -1988,7 +1988,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>41</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>43</v>
       </c>
@@ -2028,7 +2028,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>45</v>
       </c>
@@ -2045,7 +2045,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>47</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>49</v>
       </c>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="K28" s="7"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>51</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F31" t="str">
         <v>Charlie</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F32" t="str">
         <v>Eve</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>53</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F38" t="str">
         <v>Charlie</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F39" t="str">
         <v>Eve</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>55</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F45" t="str">
         <v>Diana</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>57</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F52" t="str">
         <v>Charlie</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F53" t="str">
         <v>Eve</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>58</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F59" t="str">
         <v>Eve</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>59</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>61</v>
       </c>
@@ -2339,7 +2339,7 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="6" t="s">
         <v>28</v>
       </c>
@@ -2355,7 +2355,7 @@
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="4" t="s">
         <v>62</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>64</v>
       </c>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K76" s="7"/>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>66</v>
       </c>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>68</v>
       </c>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K78" s="7"/>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>70</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F81" t="str">
         <v>Bob</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F82" t="str">
         <v>Charlie</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F83" t="str">
         <v>Diana</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F84" t="str">
         <v>Eve</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>72</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F88" t="str">
         <v>Diana</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F89" t="str">
         <v>Alice</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F90" t="str">
         <v>Charlie</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F91" t="str">
         <v>Eve</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>74</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F95" t="str">
         <v>Eve</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F96" t="str">
         <v>Alice</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F97" t="str">
         <v>Diana</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F98" t="str">
         <v>Bob</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>76</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F102" t="str">
         <v>Charlie</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F103" t="str">
         <v>Eve</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F104" t="str">
         <v>Diana</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F105" t="str">
         <v>Bob</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108" s="4" t="s">
         <v>78</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F109" t="str">
         <v>Diana</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F110" t="str">
         <v>Eve</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F111" t="str">
         <v>Alice</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F112" t="str">
         <v>Charlie</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
         <v>80</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="6" t="s">
         <v>28</v>
       </c>
@@ -2870,7 +2870,7 @@
       <c r="J117" s="11"/>
       <c r="K117" s="11"/>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="4" t="s">
         <v>81</v>
       </c>
@@ -2882,27 +2882,27 @@
         <v>Bob</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F119" t="str">
         <v>Diana</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F120" t="str">
         <v>Alice</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F121" t="str">
         <v>Charlie</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F122" t="str">
         <v>Eve</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="4" t="s">
         <v>83</v>
       </c>
@@ -2914,27 +2914,27 @@
         <v>Charlie</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F126" t="str">
         <v>Eve</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F127" t="str">
         <v>Alice</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F128" t="str">
         <v>Diana</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F129" t="str">
         <v>Bob</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132" s="4" t="s">
         <v>72</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F133" t="str">
         <v>Diana</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F134" t="str">
         <v>Alice</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F135" t="str">
         <v>Charlie</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F136" t="str">
         <v>Eve</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139" s="4" t="s">
         <v>86</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F140" t="str">
         <v>Eve</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F141" t="str">
         <v>Alice</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F142" t="str">
         <v>Diana</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F143" t="str">
         <v>Bob</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="4" t="s">
         <v>88</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>Date</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="3" t="s">
         <v>90</v>
       </c>
@@ -3126,7 +3126,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="6" t="s">
         <v>28</v>
       </c>
@@ -3142,7 +3142,7 @@
       <c r="J156" s="11"/>
       <c r="K156" s="11"/>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="4" t="s">
         <v>91</v>
       </c>
@@ -3157,17 +3157,17 @@
       <c r="H157" s="7"/>
       <c r="I157" s="7"/>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F158" t="str">
         <v>C</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F159" t="str">
         <v>B</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164" s="4" t="s">
         <v>93</v>
       </c>
@@ -3182,17 +3182,17 @@
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F165" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F166" t="str">
         <v>North</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171" s="4" t="s">
         <v>95</v>
       </c>
@@ -3207,22 +3207,22 @@
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>62</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F173">
         <v>91</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>78</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178" s="4" t="s">
         <v>97</v>
       </c>
@@ -3237,12 +3237,12 @@
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F179" t="str">
         <v>B</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>99</v>
       </c>
@@ -3257,17 +3257,17 @@
       <c r="H185" s="7"/>
       <c r="I185" s="7"/>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>62</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F187">
         <v>78</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>101</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F193" t="str">
         <v>Bob</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F194" t="str">
         <v>Charlie</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F195" t="str">
         <v>Diana</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F196" t="str">
         <v>Eve</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>103</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B206" s="3" t="s">
         <v>105</v>
       </c>
@@ -3382,7 +3382,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B208" s="6" t="s">
         <v>28</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="J208" s="11"/>
       <c r="K208" s="11"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>106</v>
       </c>
@@ -3413,27 +3413,27 @@
       <c r="H209" s="7"/>
       <c r="I209" s="7"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F211">
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F213">
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>108</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>110</v>
       </c>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I217" s="7"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>4</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F219">
         <v>7</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="s">
         <v>112</v>
       </c>
@@ -3513,27 +3513,27 @@
       <c r="H221" s="7"/>
       <c r="I221" s="7"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F222">
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F223">
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F224">
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F225">
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B227" s="4" t="s">
         <v>114</v>
       </c>
@@ -3548,27 +3548,27 @@
       <c r="H227" s="7"/>
       <c r="I227" s="7"/>
     </row>
-    <row r="228" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F229">
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F230">
         <v>16</v>
       </c>
     </row>
-    <row r="231" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F231">
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B233" s="4" t="s">
         <v>116</v>
       </c>
@@ -3583,27 +3583,27 @@
       <c r="H233" s="7"/>
       <c r="I233" s="7"/>
     </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F234">
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F235">
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F236">
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F237">
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B239" s="4" t="s">
         <v>118</v>
       </c>
@@ -3618,22 +3618,22 @@
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
     </row>
-    <row r="240" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F240">
         <v>0.25</v>
       </c>
     </row>
-    <row r="241" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F241">
         <v>0.5</v>
       </c>
     </row>
-    <row r="242" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F242">
         <v>0.75</v>
       </c>
     </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B244" s="4" t="s">
         <v>120</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F245">
         <v>5</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F246">
         <v>9</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B248" s="4" t="s">
         <v>122</v>
       </c>
@@ -3697,7 +3697,7 @@
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
     </row>
-    <row r="250" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B250" s="4" t="s">
         <v>124</v>
       </c>
@@ -3712,27 +3712,27 @@
       <c r="H250" s="7"/>
       <c r="I250" s="7"/>
     </row>
-    <row r="251" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F251">
         <v>90</v>
       </c>
     </row>
-    <row r="252" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F252">
         <v>80</v>
       </c>
     </row>
-    <row r="253" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F253">
         <v>70</v>
       </c>
     </row>
-    <row r="254" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F254">
         <v>60</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B258" s="3" t="s">
         <v>126</v>
       </c>
@@ -3746,7 +3746,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B260" s="6" t="s">
         <v>28</v>
       </c>
@@ -3762,7 +3762,7 @@
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B261" s="4" t="s">
         <v>127</v>
       </c>
@@ -3771,37 +3771,37 @@
       </c>
       <c r="F261" s="7" cm="1">
         <f t="array" aca="1" ref="F261:F265" ca="1">_xlfn.RANDARRAY(5)</f>
-        <v>0.27673750718977597</v>
+        <v>0.76135835034916899</v>
       </c>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F262">
         <f ca="1"/>
-        <v>0.61739212856712355</v>
-      </c>
-    </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.73230732159863487</v>
+      </c>
+    </row>
+    <row r="263" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F263">
         <f ca="1"/>
-        <v>0.62234151218034994</v>
-      </c>
-    </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.31983600194963469</v>
+      </c>
+    </row>
+    <row r="264" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F264">
         <f ca="1"/>
-        <v>0.34580758014841018</v>
-      </c>
-    </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.71557080299366183</v>
+      </c>
+    </row>
+    <row r="265" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F265">
         <f ca="1"/>
-        <v>0.83090176465174248</v>
-      </c>
-    </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.2">
+        <v>3.2902135333838789E-3</v>
+      </c>
+    </row>
+    <row r="267" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B267" s="4" t="s">
         <v>129</v>
       </c>
@@ -3810,26 +3810,26 @@
       </c>
       <c r="F267" s="7" cm="1">
         <f t="array" aca="1" ref="F267:J267" ca="1">_xlfn.RANDARRAY(1,5)</f>
-        <v>0.16489599988703652</v>
+        <v>0.48525660133846893</v>
       </c>
       <c r="G267" s="7">
         <f ca="1"/>
-        <v>0.17917537046567755</v>
+        <v>0.18350920144412264</v>
       </c>
       <c r="H267" s="7">
         <f ca="1"/>
-        <v>0.41745929855455466</v>
+        <v>0.28624573768475559</v>
       </c>
       <c r="I267" s="7">
         <f ca="1"/>
-        <v>8.6988428676251006E-2</v>
+        <v>0.18393599318221998</v>
       </c>
       <c r="J267">
         <f ca="1"/>
-        <v>0.77035358186580027</v>
-      </c>
-    </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.82918823360421756</v>
+      </c>
+    </row>
+    <row r="269" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B269" s="4" t="s">
         <v>131</v>
       </c>
@@ -3838,47 +3838,47 @@
       </c>
       <c r="F269" s="7" cm="1">
         <f t="array" aca="1" ref="F269:H271" ca="1">_xlfn.RANDARRAY(3,3)</f>
-        <v>0.67555775263229756</v>
+        <v>0.19787497112685415</v>
       </c>
       <c r="G269" s="7">
         <f ca="1"/>
-        <v>0.43233120398304492</v>
+        <v>0.73046970083230867</v>
       </c>
       <c r="H269" s="7">
         <f ca="1"/>
-        <v>0.60229134531189477</v>
+        <v>0.97608332940481524</v>
       </c>
       <c r="I269" s="7"/>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F270">
         <f ca="1"/>
-        <v>0.81023605578811941</v>
+        <v>0.75177581609907107</v>
       </c>
       <c r="G270">
         <f ca="1"/>
-        <v>0.75764928185757374</v>
+        <v>0.33216164893376354</v>
       </c>
       <c r="H270">
         <f ca="1"/>
-        <v>0.72640964702604194</v>
-      </c>
-    </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.46469805737966241</v>
+      </c>
+    </row>
+    <row r="271" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F271">
         <f ca="1"/>
-        <v>0.73213488902228407</v>
+        <v>0.66214610783840233</v>
       </c>
       <c r="G271">
         <f ca="1"/>
-        <v>0.60552915395738971</v>
+        <v>0.20286366014834134</v>
       </c>
       <c r="H271">
         <f ca="1"/>
-        <v>0.8581240395147407</v>
-      </c>
-    </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.55950029531342116</v>
+      </c>
+    </row>
+    <row r="273" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B273" s="4" t="s">
         <v>133</v>
       </c>
@@ -3887,37 +3887,37 @@
       </c>
       <c r="F273" s="7" cm="1">
         <f t="array" aca="1" ref="F273:F277" ca="1">_xlfn.RANDARRAY(5,1,1,100)</f>
-        <v>86.923925682498961</v>
+        <v>49.588714345944311</v>
       </c>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
     </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F274">
         <f ca="1"/>
-        <v>10.280219852028523</v>
-      </c>
-    </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.2">
+        <v>78.419023827300677</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F275">
         <f ca="1"/>
-        <v>89.803235196466829</v>
-      </c>
-    </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.2">
+        <v>10.813965768802007</v>
+      </c>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F276">
         <f ca="1"/>
-        <v>95.038961721549271</v>
-      </c>
-    </row>
-    <row r="277" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1.5484480212207927</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F277">
         <f ca="1"/>
-        <v>81.616525405990657</v>
-      </c>
-    </row>
-    <row r="279" spans="2:9" x14ac:dyDescent="0.2">
+        <v>15.484858393945643</v>
+      </c>
+    </row>
+    <row r="279" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B279" s="4" t="s">
         <v>135</v>
       </c>
@@ -3926,37 +3926,37 @@
       </c>
       <c r="F279" s="7" cm="1">
         <f t="array" aca="1" ref="F279:F283" ca="1">_xlfn.RANDARRAY(5,1,1,100,TRUE)</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
       <c r="I279" s="7"/>
     </row>
-    <row r="280" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F280">
         <f ca="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="281" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F281">
         <f ca="1"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F282">
         <f ca="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F283">
         <f ca="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="285" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B285" s="4" t="s">
         <v>137</v>
       </c>
@@ -3965,47 +3965,47 @@
       </c>
       <c r="F285" s="7" cm="1">
         <f t="array" aca="1" ref="F285:H287" ca="1">_xlfn.RANDARRAY(3,3,0,1,FALSE)</f>
-        <v>0.91785584585804325</v>
+        <v>5.9492860436057837E-2</v>
       </c>
       <c r="G285" s="7">
         <f ca="1"/>
-        <v>8.9546956258383936E-3</v>
+        <v>0.9694049966170053</v>
       </c>
       <c r="H285" s="7">
         <f ca="1"/>
-        <v>0.71935097236537238</v>
+        <v>0.42491307411750712</v>
       </c>
       <c r="I285" s="7"/>
     </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F286">
         <f ca="1"/>
-        <v>0.4763938639169667</v>
+        <v>0.85724482292397464</v>
       </c>
       <c r="G286">
         <f ca="1"/>
-        <v>6.0149353370750447E-2</v>
+        <v>0.61150710037644762</v>
       </c>
       <c r="H286">
         <f ca="1"/>
-        <v>0.42597439635954482</v>
-      </c>
-    </row>
-    <row r="287" spans="2:9" x14ac:dyDescent="0.2">
+        <v>0.66377885686919025</v>
+      </c>
+    </row>
+    <row r="287" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F287">
         <f ca="1"/>
-        <v>0.3603046257542164</v>
+        <v>0.40496182154536253</v>
       </c>
       <c r="G287">
         <f ca="1"/>
-        <v>0.26091533119145605</v>
+        <v>0.4013069865126726</v>
       </c>
       <c r="H287">
         <f ca="1"/>
-        <v>0.23687833723908636</v>
-      </c>
-    </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0.59790387964990432</v>
+      </c>
+    </row>
+    <row r="289" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B289" s="4" t="s">
         <v>139</v>
       </c>
@@ -4014,37 +4014,37 @@
       </c>
       <c r="F289" s="7" cm="1">
         <f t="array" aca="1" ref="F289:F293" ca="1">_xlfn.RANDARRAY(5,1,-10,10,TRUE)</f>
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
       <c r="I289" s="7"/>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F290">
         <f ca="1"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F291">
         <f ca="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F292">
         <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.2">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="293" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F293">
         <f ca="1"/>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B295" s="4" t="s">
         <v>141</v>
       </c>
@@ -4053,13 +4053,13 @@
       </c>
       <c r="F295" s="7" cm="1">
         <f t="array" aca="1" ref="F295" ca="1">_xlfn.RANDARRAY(1,1)</f>
-        <v>0.22820836444542758</v>
+        <v>0.69463616624644953</v>
       </c>
       <c r="G295" s="7"/>
       <c r="H295" s="7"/>
       <c r="I295" s="7"/>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B297" s="4" t="s">
         <v>143</v>
       </c>
@@ -4068,46 +4068,46 @@
       </c>
       <c r="F297" s="7" cm="1">
         <f t="array" aca="1" ref="F297:G300" ca="1">_xlfn.RANDARRAY(4,2,0,1000,TRUE)</f>
-        <v>453</v>
+        <v>739</v>
       </c>
       <c r="G297" s="7">
         <f ca="1"/>
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="H297" s="7"/>
       <c r="I297" s="7"/>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F298">
         <f ca="1"/>
-        <v>841</v>
+        <v>807</v>
       </c>
       <c r="G298">
         <f ca="1"/>
-        <v>985</v>
-      </c>
-    </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="299" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F299">
         <f ca="1"/>
-        <v>648</v>
+        <v>521</v>
       </c>
       <c r="G299">
         <f ca="1"/>
-        <v>643</v>
-      </c>
-    </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.2">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="300" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F300">
         <f ca="1"/>
-        <v>190</v>
+        <v>999</v>
       </c>
       <c r="G300">
         <f ca="1"/>
-        <v>278</v>
-      </c>
-    </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="303" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B303" s="3" t="s">
         <v>145</v>
       </c>
@@ -4121,7 +4121,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B305" s="6" t="s">
         <v>28</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="J305" s="11"/>
       <c r="K305" s="11"/>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B306" s="4" t="s">
         <v>146</v>
       </c>
@@ -4152,27 +4152,27 @@
       <c r="H306" s="7"/>
       <c r="I306" s="7"/>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F307" t="str">
         <v>Bob</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F308" t="str">
         <v>Charlie</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F309" t="str">
         <v>Diana</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F310" t="str">
         <v>Eve</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B313" s="4" t="s">
         <v>148</v>
       </c>
@@ -4187,27 +4187,27 @@
       <c r="H313" s="7"/>
       <c r="I313" s="7"/>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F314" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F315" t="str">
         <v>East</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F316" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F317" t="str">
         <v>North</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B320" s="4" t="s">
         <v>150</v>
       </c>
@@ -4224,7 +4224,7 @@
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
     </row>
-    <row r="321" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="321" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F321" t="str">
         <v>Bob</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="322" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F322" t="str">
         <v>Charlie</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="323" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F323" t="str">
         <v>Diana</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="324" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="324" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F324" t="str">
         <v>Eve</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="327" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="327" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B327" s="4" t="s">
         <v>152</v>
       </c>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I327" s="7"/>
     </row>
-    <row r="328" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F328" t="str">
         <v>West</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>Bob</v>
       </c>
     </row>
-    <row r="329" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F329" t="str">
         <v>East</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>Charlie</v>
       </c>
     </row>
-    <row r="330" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F330" t="str">
         <v>West</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>Diana</v>
       </c>
     </row>
-    <row r="331" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="331" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F331" t="str">
         <v>North</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>Eve</v>
       </c>
     </row>
-    <row r="334" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="334" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B334" s="4" t="s">
         <v>154</v>
       </c>
@@ -4334,27 +4334,27 @@
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
     </row>
-    <row r="335" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="335" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F335" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="336" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F336" t="str">
         <v>East</v>
       </c>
     </row>
-    <row r="337" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F337" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="338" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F338" t="str">
         <v>North</v>
       </c>
     </row>
-    <row r="341" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="341" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B341" s="4" t="s">
         <v>156</v>
       </c>
@@ -4371,7 +4371,7 @@
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
     </row>
-    <row r="342" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="342" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F342" t="str">
         <v>C</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="343" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F343" t="str">
         <v>A</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="344" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F344" t="str">
         <v>B</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="345" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F345" t="str">
         <v>A</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="348" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="348" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B348" s="4" t="s">
         <v>158</v>
       </c>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="I348" s="7"/>
     </row>
-    <row r="349" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F349" t="str">
         <v>Bob</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>Bob</v>
       </c>
     </row>
-    <row r="350" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="350" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F350" t="str">
         <v>Charlie</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>Charlie</v>
       </c>
     </row>
-    <row r="351" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="351" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F351" t="str">
         <v>Diana</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>Diana</v>
       </c>
     </row>
-    <row r="352" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F352" t="str">
         <v>Eve</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>Eve</v>
       </c>
     </row>
-    <row r="357" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B357" s="3" t="s">
         <v>160</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
     </row>
-    <row r="359" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B359" s="6" t="s">
         <v>28</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="J359" s="11"/>
       <c r="K359" s="11"/>
     </row>
-    <row r="360" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B360" s="4" t="s">
         <v>161</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="362" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B362" s="4" t="s">
         <v>163</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="364" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B364" s="4" t="s">
         <v>165</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="365" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F365" t="str">
         <v>Charlie</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="366" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F366" t="str">
         <v>Eve</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="368" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B368" s="4" t="s">
         <v>167</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="369" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F369" t="str">
         <v>Charlie</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="370" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F370" t="str">
         <v>Alice</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B372" s="4" t="s">
         <v>154</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="374" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B374" s="4" t="s">
         <v>170</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="375" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F375" t="str">
         <v>Diana</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="376" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F376" t="str">
         <v>Charlie</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="378" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B378" s="4" t="s">
         <v>172</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="379" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F379" t="str">
         <v>Alice</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B382" s="3" t="s">
         <v>174</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
     </row>
-    <row r="384" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B384" s="6" t="s">
         <v>28</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="J384" s="11"/>
       <c r="K384" s="11"/>
     </row>
-    <row r="385" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B385" s="4" t="s">
         <v>175</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>Elderberry</v>
       </c>
     </row>
-    <row r="387" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B387" s="4" t="s">
         <v>177</v>
       </c>
@@ -4829,7 +4829,7 @@
       <c r="J387" s="7"/>
       <c r="K387" s="7"/>
     </row>
-    <row r="388" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F388" t="str">
         <v>Bob</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="389" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F389" t="str">
         <v>Charlie</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="390" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F390" t="str">
         <v>Diana</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="391" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F391" t="str">
         <v>Eve</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="394" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B394" s="4" t="s">
         <v>179</v>
       </c>
@@ -4882,7 +4882,7 @@
       <c r="J394" s="7"/>
       <c r="K394" s="7"/>
     </row>
-    <row r="395" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F395" t="str">
         <v>Bob</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="396" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F396" t="str">
         <v>Charlie</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="397" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F397" t="str">
         <v>Diana</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="398" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F398" t="str">
         <v>Eve</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="401" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B401" s="4" t="s">
         <v>181</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="403" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B403" s="4" t="s">
         <v>183</v>
       </c>
@@ -4972,7 +4972,7 @@
       <c r="J403" s="7"/>
       <c r="K403" s="7"/>
     </row>
-    <row r="404" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F404" t="str">
         <v>Bob</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="405" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F405" t="str">
         <v>Charlie</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="406" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F406" t="e">
         <v>#N/A</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="407" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F407" t="e">
         <v>#N/A</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="410" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B410" s="4" t="s">
         <v>185</v>
       </c>
@@ -5025,7 +5025,7 @@
       <c r="J410" s="7"/>
       <c r="K410" s="7"/>
     </row>
-    <row r="411" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F411" t="str">
         <v>Bob</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="412" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F412" t="str">
         <v>Charlie</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="413" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F413" t="str">
         <v>Diana</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="414" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F414" t="str">
         <v>Eve</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="419" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B419" s="3" t="s">
         <v>187</v>
       </c>
@@ -5083,7 +5083,7 @@
       <c r="J419" s="3"/>
       <c r="K419" s="3"/>
     </row>
-    <row r="421" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B421" s="6" t="s">
         <v>28</v>
       </c>
@@ -5099,7 +5099,7 @@
       <c r="J421" s="11"/>
       <c r="K421" s="11"/>
     </row>
-    <row r="422" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B422" s="4" t="s">
         <v>188</v>
       </c>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="K422" s="7"/>
     </row>
-    <row r="423" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F423" t="str">
         <v>Apple</v>
       </c>
@@ -5141,7 +5141,7 @@
         <v>Elderberry</v>
       </c>
     </row>
-    <row r="425" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B425" s="4" t="s">
         <v>190</v>
       </c>
@@ -5164,7 +5164,7 @@
       <c r="J425" s="7"/>
       <c r="K425" s="7"/>
     </row>
-    <row r="426" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F426" t="str">
         <v>Bob</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="427" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F427" t="str">
         <v>Diana</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="428" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F428" t="str">
         <v>Eve</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="430" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B430" s="4" t="s">
         <v>192</v>
       </c>
@@ -5229,7 +5229,7 @@
       <c r="J430" s="7"/>
       <c r="K430" s="7"/>
     </row>
-    <row r="431" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F431" t="str">
         <v>Charlie</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="432" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F432" t="str">
         <v>Eve</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="434" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="434" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B434" s="4" t="s">
         <v>181</v>
       </c>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="K434" s="7"/>
     </row>
-    <row r="435" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="435" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F435">
         <v>100</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="437" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="437" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B437" s="4" t="s">
         <v>195</v>
       </c>
@@ -5322,7 +5322,7 @@
       <c r="J437" s="7"/>
       <c r="K437" s="7"/>
     </row>
-    <row r="438" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="438" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F438" t="str">
         <v>Bob</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="439" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="439" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F439" t="str">
         <v>Diana</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="440" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="440" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F440" t="str">
         <v>Eve</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="442" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="442" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B442" s="4" t="s">
         <v>197</v>
       </c>
@@ -5387,7 +5387,7 @@
       <c r="J442" s="7"/>
       <c r="K442" s="7"/>
     </row>
-    <row r="443" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="443" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F443" t="str">
         <v>Bob</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="444" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="444" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F444" t="str">
         <v>Alice</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="445" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="445" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F445" t="str">
         <v>Bob</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="448" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="448" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B448" s="3" t="s">
         <v>199</v>
       </c>
@@ -5443,7 +5443,7 @@
       <c r="J448" s="3"/>
       <c r="K448" s="3"/>
     </row>
-    <row r="450" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="450" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B450" s="6" t="s">
         <v>28</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="J450" s="11"/>
       <c r="K450" s="11"/>
     </row>
-    <row r="451" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="451" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B451" s="4" t="s">
         <v>200</v>
       </c>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K451" s="7"/>
     </row>
-    <row r="453" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="453" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B453" s="4" t="s">
         <v>202</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="455" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="455" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B455" s="4" t="s">
         <v>204</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="457" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="457" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B457" s="4" t="s">
         <v>206</v>
       </c>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="K457" s="7"/>
     </row>
-    <row r="459" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="459" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B459" s="4" t="s">
         <v>208</v>
       </c>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="K459" s="7"/>
     </row>
-    <row r="461" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="461" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B461" s="4" t="s">
         <v>210</v>
       </c>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="K461" s="7"/>
     </row>
-    <row r="465" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="465" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B465" s="3" t="s">
         <v>212</v>
       </c>
@@ -5627,7 +5627,7 @@
       <c r="J465" s="3"/>
       <c r="K465" s="3"/>
     </row>
-    <row r="467" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="467" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B467" s="6" t="s">
         <v>28</v>
       </c>
@@ -5643,7 +5643,7 @@
       <c r="J467" s="11"/>
       <c r="K467" s="11"/>
     </row>
-    <row r="468" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="468" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B468" s="4" t="s">
         <v>213</v>
       </c>
@@ -5660,27 +5660,27 @@
       <c r="J468" s="7"/>
       <c r="K468" s="7"/>
     </row>
-    <row r="469" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="469" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F469">
         <v>25</v>
       </c>
     </row>
-    <row r="470" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="470" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F470">
         <v>-5</v>
       </c>
     </row>
-    <row r="471" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="471" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F471">
         <v>42.5</v>
       </c>
     </row>
-    <row r="472" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="472" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F472">
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="475" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B475" s="4" t="s">
         <v>215</v>
       </c>
@@ -5697,32 +5697,32 @@
       <c r="J475" s="7"/>
       <c r="K475" s="7"/>
     </row>
-    <row r="476" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="476" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F476">
         <v>85</v>
       </c>
     </row>
-    <row r="477" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="477" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F477" t="str">
         <v>Bob</v>
       </c>
     </row>
-    <row r="478" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="478" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F478">
         <v>62</v>
       </c>
     </row>
-    <row r="479" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="479" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F479" t="str">
         <v>Charlie</v>
       </c>
     </row>
-    <row r="480" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="480" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F480">
         <v>91</v>
       </c>
     </row>
-    <row r="483" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="483" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B483" s="4" t="s">
         <v>216</v>
       </c>
@@ -5739,32 +5739,32 @@
       <c r="J483" s="7"/>
       <c r="K483" s="7"/>
     </row>
-    <row r="484" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="484" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F484" t="str">
         <v>Bob</v>
       </c>
     </row>
-    <row r="485" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="485" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F485" t="str">
         <v>Charlie</v>
       </c>
     </row>
-    <row r="486" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="486" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F486">
         <v>85</v>
       </c>
     </row>
-    <row r="487" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F487">
         <v>62</v>
       </c>
     </row>
-    <row r="488" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F488">
         <v>91</v>
       </c>
     </row>
-    <row r="491" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B491" s="4" t="s">
         <v>206</v>
       </c>
@@ -5781,27 +5781,27 @@
       <c r="J491" s="7"/>
       <c r="K491" s="7"/>
     </row>
-    <row r="492" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F492">
         <v>25</v>
       </c>
     </row>
-    <row r="493" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F493">
         <v>-5</v>
       </c>
     </row>
-    <row r="494" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F494">
         <v>42.5</v>
       </c>
     </row>
-    <row r="495" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F495">
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B498" s="4" t="s">
         <v>208</v>
       </c>
@@ -5818,27 +5818,27 @@
       <c r="J498" s="7"/>
       <c r="K498" s="7"/>
     </row>
-    <row r="499" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F499">
         <v>25</v>
       </c>
     </row>
-    <row r="500" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F500">
         <v>-5</v>
       </c>
     </row>
-    <row r="501" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F501">
         <v>42.5</v>
       </c>
     </row>
-    <row r="502" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F502">
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="507" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B507" s="3" t="s">
         <v>217</v>
       </c>
@@ -5852,7 +5852,7 @@
       <c r="J507" s="3"/>
       <c r="K507" s="3"/>
     </row>
-    <row r="509" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B509" s="6" t="s">
         <v>28</v>
       </c>
@@ -5868,7 +5868,7 @@
       <c r="J509" s="11"/>
       <c r="K509" s="11"/>
     </row>
-    <row r="510" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B510" s="4" t="s">
         <v>218</v>
       </c>
@@ -5891,7 +5891,7 @@
       <c r="J510" s="7"/>
       <c r="K510" s="7"/>
     </row>
-    <row r="511" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F511" t="str">
         <v>Bob</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="513" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B513" s="4" t="s">
         <v>220</v>
       </c>
@@ -5928,7 +5928,7 @@
       <c r="J513" s="7"/>
       <c r="K513" s="7"/>
     </row>
-    <row r="514" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F514" t="str">
         <v>Eve</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="516" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B516" s="4" t="s">
         <v>222</v>
       </c>
@@ -5961,7 +5961,7 @@
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
     </row>
-    <row r="517" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F517" t="str">
         <v>Bob</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="518" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="518" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F518" t="str">
         <v>Charlie</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="519" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="519" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F519" t="str">
         <v>Diana</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="520" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="520" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F520" t="str">
         <v>Eve</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="523" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="523" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B523" s="4" t="s">
         <v>224</v>
       </c>
@@ -6010,27 +6010,27 @@
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
     </row>
-    <row r="524" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="524" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F524" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="525" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="525" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F525" t="str">
         <v>East</v>
       </c>
     </row>
-    <row r="526" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="526" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F526" t="str">
         <v>West</v>
       </c>
     </row>
-    <row r="527" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="527" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F527" t="str">
         <v>North</v>
       </c>
     </row>
-    <row r="530" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="530" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B530" s="4" t="s">
         <v>226</v>
       </c>
@@ -6049,7 +6049,7 @@
       <c r="J530" s="7"/>
       <c r="K530" s="7"/>
     </row>
-    <row r="531" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="531" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F531" t="str">
         <v>Bob</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="533" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="533" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B533" s="4" t="s">
         <v>228</v>
       </c>
@@ -6074,7 +6074,7 @@
       <c r="J533" s="7"/>
       <c r="K533" s="7"/>
     </row>
-    <row r="535" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="535" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B535" s="4" t="s">
         <v>230</v>
       </c>
@@ -6093,7 +6093,7 @@
       <c r="J535" s="7"/>
       <c r="K535" s="7"/>
     </row>
-    <row r="536" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="536" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F536" t="str">
         <v>C</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="537" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="537" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F537" t="str">
         <v>A</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="539" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="539" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B539" s="4" t="s">
         <v>232</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="J539" s="7"/>
       <c r="K539" s="7"/>
     </row>
-    <row r="541" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="541" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B541" s="4" t="s">
         <v>234</v>
       </c>
@@ -6149,7 +6149,7 @@
       <c r="J541" s="7"/>
       <c r="K541" s="7"/>
     </row>
-    <row r="545" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="545" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B545" s="3" t="s">
         <v>236</v>
       </c>
@@ -6163,7 +6163,7 @@
       <c r="J545" s="3"/>
       <c r="K545" s="3"/>
     </row>
-    <row r="547" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="547" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B547" s="6" t="s">
         <v>28</v>
       </c>
@@ -6179,7 +6179,7 @@
       <c r="J547" s="11"/>
       <c r="K547" s="11"/>
     </row>
-    <row r="548" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="548" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B548" s="4" t="s">
         <v>237</v>
       </c>
@@ -6202,7 +6202,7 @@
       <c r="J548" s="7"/>
       <c r="K548" s="7"/>
     </row>
-    <row r="549" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F549" t="str">
         <v>Diana</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="550" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F550" t="str">
         <v>Eve</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="552" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B552" s="4" t="s">
         <v>239</v>
       </c>
@@ -6253,7 +6253,7 @@
       <c r="J552" s="7"/>
       <c r="K552" s="7"/>
     </row>
-    <row r="553" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F553" t="str">
         <v>Bob</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="554" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F554" t="str">
         <v>Charlie</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="556" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B556" s="4" t="s">
         <v>241</v>
       </c>
@@ -6302,7 +6302,7 @@
       <c r="J556" s="7"/>
       <c r="K556" s="7"/>
     </row>
-    <row r="557" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F557">
         <v>62</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="558" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F558">
         <v>91</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>East</v>
       </c>
     </row>
-    <row r="559" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F559">
         <v>78</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="560" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F560">
         <v>91</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="563" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B563" s="4" t="s">
         <v>243</v>
       </c>
@@ -6367,7 +6367,7 @@
       <c r="J563" s="7"/>
       <c r="K563" s="7"/>
     </row>
-    <row r="564" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F564" t="str">
         <v>Bob</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="565" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F565" t="str">
         <v>Charlie</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="566" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F566" t="str">
         <v>Diana</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="567" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F567" t="str">
         <v>Eve</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="570" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="570" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B570" s="4" t="s">
         <v>245</v>
       </c>
@@ -6432,7 +6432,7 @@
       <c r="J570" s="7"/>
       <c r="K570" s="7"/>
     </row>
-    <row r="571" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F571">
         <v>78</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>West</v>
       </c>
     </row>
-    <row r="572" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F572">
         <v>91</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>North</v>
       </c>
     </row>
-    <row r="574" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="574" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B574" s="4" t="s">
         <v>228</v>
       </c>
@@ -6475,7 +6475,7 @@
       <c r="J574" s="7"/>
       <c r="K574" s="7"/>
     </row>
-    <row r="575" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F575" t="str">
         <v>Bob</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="576" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F576" t="str">
         <v>Charlie</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="577" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="577" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F577" t="str">
         <v>Diana</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="579" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="579" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B579" s="4" t="s">
         <v>248</v>
       </c>
@@ -6529,7 +6529,7 @@
       <c r="J579" s="7"/>
       <c r="K579" s="7"/>
     </row>
-    <row r="581" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="581" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B581" s="4" t="s">
         <v>250</v>
       </c>
@@ -6548,7 +6548,7 @@
       <c r="J581" s="7"/>
       <c r="K581" s="7"/>
     </row>
-    <row r="584" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="584" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B584" s="3" t="s">
         <v>252</v>
       </c>
@@ -6562,7 +6562,7 @@
       <c r="J584" s="3"/>
       <c r="K584" s="3"/>
     </row>
-    <row r="586" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="586" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B586" s="6" t="s">
         <v>28</v>
       </c>
@@ -6578,7 +6578,7 @@
       <c r="J586" s="11"/>
       <c r="K586" s="11"/>
     </row>
-    <row r="587" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="587" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B587" s="4" t="s">
         <v>253</v>
       </c>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="K587" s="7"/>
     </row>
-    <row r="589" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="589" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B589" s="4" t="s">
         <v>255</v>
       </c>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K589" s="7"/>
     </row>
-    <row r="591" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="591" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B591" s="4" t="s">
         <v>257</v>
       </c>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K591" s="7"/>
     </row>
-    <row r="593" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="593" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B593" s="4" t="s">
         <v>259</v>
       </c>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="K593" s="7"/>
     </row>
-    <row r="595" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="595" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B595" s="4" t="s">
         <v>261</v>
       </c>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="K595" s="7"/>
     </row>
-    <row r="597" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="597" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B597" s="4" t="s">
         <v>263</v>
       </c>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="K597" s="7"/>
     </row>
-    <row r="599" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="599" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B599" s="4" t="s">
         <v>265</v>
       </c>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="K599" s="7"/>
     </row>
-    <row r="601" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="601" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B601" s="4" t="s">
         <v>267</v>
       </c>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="K601" s="7"/>
     </row>
-    <row r="603" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="603" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B603" s="4" t="s">
         <v>268</v>
       </c>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="K603" s="7"/>
     </row>
-    <row r="605" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="605" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B605" s="4" t="s">
         <v>270</v>
       </c>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="K605" s="7"/>
     </row>
-    <row r="607" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="607" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B607" s="4" t="s">
         <v>280</v>
       </c>
@@ -6845,27 +6845,27 @@
       <c r="J607" s="7"/>
       <c r="K607" s="7"/>
     </row>
-    <row r="608" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="608" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F608">
         <v>68</v>
       </c>
     </row>
-    <row r="609" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="609" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F609">
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="610" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F610">
         <v>86</v>
       </c>
     </row>
-    <row r="611" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="611" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F611">
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="615" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B615" s="3" t="s">
         <v>271</v>
       </c>
@@ -6879,7 +6879,7 @@
       <c r="J615" s="3"/>
       <c r="K615" s="3"/>
     </row>
-    <row r="617" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B617" s="6" t="s">
         <v>28</v>
       </c>
@@ -6895,7 +6895,7 @@
       <c r="J617" s="11"/>
       <c r="K617" s="11"/>
     </row>
-    <row r="618" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="618" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B618" s="4" t="s">
         <v>272</v>
       </c>
@@ -6912,7 +6912,7 @@
       <c r="J618" s="11"/>
       <c r="K618" s="11"/>
     </row>
-    <row r="619" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="619" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B619" s="4" t="s">
         <v>272</v>
       </c>
@@ -6929,7 +6929,7 @@
       <c r="J619" s="7"/>
       <c r="K619" s="7"/>
     </row>
-    <row r="620" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="620" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B620" s="4" t="s">
         <v>274</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="621" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B621" s="4" t="s">
         <v>274</v>
       </c>
@@ -6958,7 +6958,7 @@
       <c r="J621" s="7"/>
       <c r="K621" s="7"/>
     </row>
-    <row r="622" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="622" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B622" s="4" t="s">
         <v>276</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="623" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="623" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B623" t="s">
         <v>276</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="624" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="624" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B624" s="4" t="s">
         <v>282</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="626" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="626" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B626" s="4" t="s">
         <v>284</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="628" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="628" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B628" s="4" t="s">
         <v>286</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>Apple, Banana, Cherry, Date, Elderberry</v>
       </c>
     </row>
-    <row r="630" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="630" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B630" s="4" t="s">
         <v>288</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>2556.25</v>
       </c>
     </row>
-    <row r="632" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="632" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B632" s="4" t="s">
         <v>290</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="635" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B635" s="3" t="s">
         <v>292</v>
       </c>
@@ -7052,7 +7052,7 @@
       <c r="J635" s="3"/>
       <c r="K635" s="3"/>
     </row>
-    <row r="637" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="637" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B637" s="6" t="s">
         <v>28</v>
       </c>
@@ -7068,7 +7068,7 @@
       <c r="J637" s="11"/>
       <c r="K637" s="11"/>
     </row>
-    <row r="638" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="638" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B638" s="4" t="s">
         <v>293</v>
       </c>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="K638" s="7"/>
     </row>
-    <row r="640" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="640" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B640" s="4" t="s">
         <v>295</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K640" s="7"/>
     </row>
-    <row r="642" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="642" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B642" s="4" t="s">
         <v>297</v>
       </c>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="K642" s="7"/>
     </row>
-    <row r="644" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="644" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B644" s="4" t="s">
         <v>299</v>
       </c>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="K644" s="7"/>
     </row>
-    <row r="646" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="646" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B646" s="4" t="s">
         <v>301</v>
       </c>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="K646" s="7"/>
     </row>
-    <row r="648" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="648" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B648" s="4" t="s">
         <v>303</v>
       </c>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="K648" s="7"/>
     </row>
-    <row r="650" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="650" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B650" s="4" t="s">
         <v>305</v>
       </c>
@@ -7235,27 +7235,27 @@
       <c r="J650" s="7"/>
       <c r="K650" s="7"/>
     </row>
-    <row r="651" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="651" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F651">
         <v>147</v>
       </c>
     </row>
-    <row r="652" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="652" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F652">
         <v>238</v>
       </c>
     </row>
-    <row r="653" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="653" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F653">
         <v>316</v>
       </c>
     </row>
-    <row r="654" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="654" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F654">
         <v>407</v>
       </c>
     </row>
-    <row r="658" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="658" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B658" s="3" t="s">
         <v>307</v>
       </c>
@@ -7269,7 +7269,7 @@
       <c r="J658" s="3"/>
       <c r="K658" s="3"/>
     </row>
-    <row r="660" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="660" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B660" s="6" t="s">
         <v>28</v>
       </c>
@@ -7285,7 +7285,7 @@
       <c r="J660" s="11"/>
       <c r="K660" s="11"/>
     </row>
-    <row r="661" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="661" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B661" s="4" t="s">
         <v>308</v>
       </c>
@@ -7302,7 +7302,7 @@
       <c r="J661" s="7"/>
       <c r="K661" s="7"/>
     </row>
-    <row r="663" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="663" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B663" s="4" t="s">
         <v>310</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="J663" s="7"/>
       <c r="K663" s="7"/>
     </row>
-    <row r="665" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="665" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B665" s="4" t="s">
         <v>312</v>
       </c>
@@ -7336,7 +7336,7 @@
       <c r="J665" s="7"/>
       <c r="K665" s="7"/>
     </row>
-    <row r="667" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="667" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B667" s="4" t="s">
         <v>314</v>
       </c>
@@ -7353,7 +7353,7 @@
       <c r="J667" s="7"/>
       <c r="K667" s="7"/>
     </row>
-    <row r="669" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="669" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B669" s="4" t="s">
         <v>316</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="J669" s="7"/>
       <c r="K669" s="7"/>
     </row>
-    <row r="671" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="671" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B671" s="4" t="s">
         <v>318</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="J671" s="7"/>
       <c r="K671" s="7"/>
     </row>
-    <row r="673" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="673" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B673" s="4" t="s">
         <v>320</v>
       </c>
@@ -7404,7 +7404,7 @@
       <c r="J673" s="7"/>
       <c r="K673" s="7"/>
     </row>
-    <row r="675" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="675" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B675" s="4" t="s">
         <v>322</v>
       </c>
@@ -7421,7 +7421,7 @@
       <c r="J675" s="7"/>
       <c r="K675" s="7"/>
     </row>
-    <row r="677" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="677" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B677" s="4" t="s">
         <v>324</v>
       </c>
@@ -7438,7 +7438,7 @@
       <c r="J677" s="7"/>
       <c r="K677" s="7"/>
     </row>
-    <row r="679" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="679" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B679" s="4" t="s">
         <v>326</v>
       </c>
@@ -7455,7 +7455,7 @@
       <c r="J679" s="7"/>
       <c r="K679" s="7"/>
     </row>
-    <row r="681" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="681" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B681" s="4" t="s">
         <v>328</v>
       </c>
@@ -7472,7 +7472,7 @@
       <c r="J681" s="7"/>
       <c r="K681" s="7"/>
     </row>
-    <row r="683" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="683" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B683" s="4" t="s">
         <v>330</v>
       </c>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="K683" s="7"/>
     </row>
-    <row r="685" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="685" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B685" s="4" t="s">
         <v>332</v>
       </c>
@@ -7514,7 +7514,7 @@
       <c r="J685" s="7"/>
       <c r="K685" s="7"/>
     </row>
-    <row r="687" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="687" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B687" s="4" t="s">
         <v>334</v>
       </c>
@@ -7531,7 +7531,7 @@
       <c r="J687" s="7"/>
       <c r="K687" s="7"/>
     </row>
-    <row r="689" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="689" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B689" s="4" t="s">
         <v>336</v>
       </c>
@@ -7548,12 +7548,12 @@
       <c r="J689" s="7"/>
       <c r="K689" s="7"/>
     </row>
-    <row r="692" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="692" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B692" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="693" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B693" s="13" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="694" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="694" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B694" s="13" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="695" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="695" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B695" s="13" t="e">
         <v>#VALUE!</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="696" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="696" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B696" s="13" t="e">
         <v>#N/A</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="697" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="697" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B697" s="13" t="e">
         <v>#NUM!</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="698" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="698" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B698" s="13" t="e">
         <v>#NAME?</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="699" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="699" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B699" s="13" t="s">
         <v>1</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="700" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="700" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B700" s="13" t="s">
         <v>345</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="701" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="701" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B701" s="13" t="s">
         <v>307</v>
       </c>
